--- a/data/trans_orig/IP19D-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP19D-Clase-trans_orig.xlsx
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27994</t>
+          <t>27684</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39463</t>
+          <t>39088</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26715</t>
+          <t>26055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37035</t>
+          <t>36407</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57774</t>
+          <t>57175</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72627</t>
+          <t>72957</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>70,05%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7889</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14941</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11875</t>
+          <t>12287</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22541</t>
+          <t>23304</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17996</t>
+          <t>17881</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23271</t>
+          <t>22525</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37366</t>
+          <t>37462</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,97%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16481</t>
+          <t>16926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26694</t>
+          <t>27092</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18216</t>
+          <t>18187</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27339</t>
+          <t>27766</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38312</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52350</t>
+          <t>51837</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>66,85%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>9657</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20469</t>
+          <t>19871</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16926</t>
+          <t>16798</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20130</t>
+          <t>20370</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33836</t>
+          <t>33386</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,05%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18066</t>
+          <t>17735</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26592</t>
+          <t>26691</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26153</t>
+          <t>25679</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36872</t>
+          <t>36512</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>46542</t>
+          <t>45977</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>60842</t>
+          <t>60437</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15831</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>12785</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23205</t>
+          <t>23665</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22102</t>
+          <t>22767</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36152</t>
+          <t>36983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57743</t>
+          <t>57409</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71994</t>
+          <t>72360</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53771</t>
+          <t>53394</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68845</t>
+          <t>68553</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>115179</t>
+          <t>114796</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>135612</t>
+          <t>135409</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>22811</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37103</t>
+          <t>37236</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26067</t>
+          <t>25740</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40791</t>
+          <t>40758</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53255</t>
+          <t>53550</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73919</t>
+          <t>74357</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,67%</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>6216</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24775</t>
+          <t>25914</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>37279</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>36593</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49927</t>
+          <t>49690</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>66381</t>
+          <t>66338</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84162</t>
+          <t>83488</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15751</t>
+          <t>15338</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26970</t>
+          <t>26778</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>18311</t>
+          <t>18297</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>30921</t>
+          <t>31370</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>36527</t>
+          <t>36964</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>54225</t>
+          <t>53896</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>20583</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29410</t>
+          <t>29324</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15787</t>
+          <t>15720</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24993</t>
+          <t>24569</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38480</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>15630</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17367</t>
+          <t>17273</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>16534</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>30050</t>
+          <t>30172</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>14460</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>184815</t>
+          <t>186890</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>213893</t>
+          <t>214364</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>196408</t>
+          <t>197102</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>224642</t>
+          <t>225166</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>390874</t>
+          <t>392550</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>431406</t>
+          <t>429616</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,62%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>16063</t>
+          <t>15550</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12495</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>26237</t>
+          <t>26411</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>91610</t>
+          <t>91662</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>119543</t>
+          <t>118026</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>99634</t>
+          <t>98667</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>127049</t>
+          <t>126087</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>198393</t>
+          <t>198980</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>236598</t>
+          <t>236466</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -5063,12 +5063,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>25305</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36727</t>
+          <t>36747</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23246</t>
+          <t>23192</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32476</t>
+          <t>32217</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51869</t>
+          <t>52023</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67293</t>
+          <t>67143</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21577</t>
+          <t>21695</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13077</t>
+          <t>12739</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17719</t>
+          <t>17825</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31448</t>
+          <t>31472</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5632,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20695</t>
+          <t>20719</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32003</t>
+          <t>31847</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21018</t>
+          <t>19935</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32716</t>
+          <t>32101</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43982</t>
+          <t>43823</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60204</t>
+          <t>61084</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11104</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12111</t>
+          <t>12234</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23050</t>
+          <t>23165</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>16079</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26848</t>
+          <t>28245</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31071</t>
+          <t>29947</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46501</t>
+          <t>46768</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,26%</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16983</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27402</t>
+          <t>27089</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16055</t>
+          <t>16249</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26325</t>
+          <t>26707</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>36064</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>50935</t>
+          <t>50500</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,49%</t>
         </is>
       </c>
     </row>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24809</t>
+          <t>24705</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>12379</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22100</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28493</t>
+          <t>29216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43100</t>
+          <t>43829</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29514</t>
+          <t>29058</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44107</t>
+          <t>44195</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25214</t>
+          <t>24483</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39840</t>
+          <t>39818</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>58989</t>
+          <t>58766</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80342</t>
+          <t>81183</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>757</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>10535</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14599</t>
+          <t>15419</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41008</t>
+          <t>41224</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55833</t>
+          <t>56476</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48381</t>
+          <t>48773</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64661</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93372</t>
+          <t>92472</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>116183</t>
+          <t>115707</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>619</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29499</t>
+          <t>28325</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44292</t>
+          <t>44007</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26819</t>
+          <t>27086</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41997</t>
+          <t>41247</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59245</t>
+          <t>60321</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>81069</t>
+          <t>81680</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,39%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>620</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>36557</t>
+          <t>36747</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>51344</t>
+          <t>52113</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>28265</t>
+          <t>28619</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>42690</t>
+          <t>41938</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>69867</t>
+          <t>69671</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>91387</t>
+          <t>90585</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,11%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10412</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18551</t>
+          <t>18813</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16179</t>
+          <t>16086</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25986</t>
+          <t>26383</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>29602</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>42183</t>
+          <t>41913</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>66,97%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15278</t>
+          <t>15273</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10328</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>20324</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>20196</t>
+          <t>20149</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>32760</t>
+          <t>33435</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>53,42%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12718</t>
+          <t>13581</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>19527</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>153165</t>
+          <t>153936</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>182567</t>
+          <t>183772</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>147313</t>
+          <t>149152</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>177897</t>
+          <t>180642</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>310679</t>
+          <t>307781</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>353277</t>
+          <t>350298</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,65%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13060</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>10805</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>23644</t>
+          <t>24257</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>17098</t>
+          <t>16834</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>32293</t>
+          <t>32163</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>142214</t>
+          <t>141660</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>172054</t>
+          <t>170871</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>139985</t>
+          <t>138829</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>170533</t>
+          <t>168427</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>288912</t>
+          <t>290171</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>332033</t>
+          <t>333090</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,11%</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9252,12 +9252,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -9280,12 +9280,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21133</t>
+          <t>21250</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31844</t>
+          <t>31815</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23880</t>
+          <t>23829</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35113</t>
+          <t>35362</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48773</t>
+          <t>48829</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64886</t>
+          <t>65285</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>70,29%</t>
         </is>
       </c>
     </row>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9394</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>575</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>11799</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -9506,12 +9506,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15294</t>
+          <t>15603</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23409</t>
+          <t>22860</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20426</t>
+          <t>20335</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35568</t>
+          <t>35161</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>37,86%</t>
         </is>
       </c>
     </row>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9806,12 +9806,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -9849,12 +9849,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28389</t>
+          <t>28365</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40141</t>
+          <t>39717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27184</t>
+          <t>27878</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38808</t>
+          <t>39205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59826</t>
+          <t>59102</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75925</t>
+          <t>75455</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,1%</t>
         </is>
       </c>
     </row>
@@ -9962,12 +9962,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12146</t>
+          <t>11746</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13164</t>
+          <t>14094</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -10075,12 +10075,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16633</t>
+          <t>16800</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11124</t>
+          <t>10830</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22895</t>
+          <t>22468</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>20718</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35929</t>
+          <t>36207</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -10418,12 +10418,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15537</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24590</t>
+          <t>24328</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10433,12 +10433,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13735</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22729</t>
+          <t>22818</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>32104</t>
+          <t>31954</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>44929</t>
+          <t>45086</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,73%</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>576</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -10644,12 +10644,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14876</t>
+          <t>14255</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10659,12 +10659,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16122</t>
+          <t>15716</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15130</t>
+          <t>14794</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28168</t>
+          <t>27632</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,12%</t>
         </is>
       </c>
     </row>
@@ -10874,12 +10874,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10959,12 +10959,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50766</t>
+          <t>50113</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67456</t>
+          <t>67947</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47262</t>
+          <t>46519</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64749</t>
+          <t>62984</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101904</t>
+          <t>101130</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>125574</t>
+          <t>125625</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11072,12 +11072,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,84%</t>
         </is>
       </c>
     </row>
@@ -11100,12 +11100,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -11213,12 +11213,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36484</t>
+          <t>35651</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52881</t>
+          <t>52205</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34121</t>
+          <t>35416</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51663</t>
+          <t>51504</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11263,12 +11263,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>75993</t>
+          <t>76761</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99424</t>
+          <t>100738</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,98%</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31700</t>
+          <t>31787</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44962</t>
+          <t>44611</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31360</t>
+          <t>30912</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46453</t>
+          <t>45803</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>66890</t>
+          <t>66410</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>86872</t>
+          <t>85817</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>59,75%</t>
         </is>
       </c>
     </row>
@@ -11782,12 +11782,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22982</t>
+          <t>23592</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>37008</t>
+          <t>36496</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11797,12 +11797,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11817,12 +11817,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>27124</t>
+          <t>27196</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>41917</t>
+          <t>41680</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11832,12 +11832,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>53753</t>
+          <t>55405</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>74583</t>
+          <t>74224</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11867,12 +11867,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,67%</t>
         </is>
       </c>
     </row>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12032,7 +12032,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -12125,12 +12125,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>18563</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26954</t>
+          <t>26929</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12160,12 +12160,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16353</t>
+          <t>16605</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25646</t>
+          <t>25755</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12195,12 +12195,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>38214</t>
+          <t>38759</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>50829</t>
+          <t>50468</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>78,81%</t>
         </is>
       </c>
     </row>
@@ -12351,12 +12351,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>5835</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>14577</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>11879</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>23970</t>
+          <t>23114</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>36,09%</t>
         </is>
       </c>
     </row>
@@ -12581,12 +12581,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12918</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12616,12 +12616,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12764</t>
+          <t>13690</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10114</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>22688</t>
+          <t>22919</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12666,12 +12666,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -12694,12 +12694,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>187247</t>
+          <t>186988</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>216554</t>
+          <t>216847</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12729,12 +12729,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>182272</t>
+          <t>181659</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>212793</t>
+          <t>212159</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12764,12 +12764,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>378414</t>
+          <t>376398</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>420039</t>
+          <t>418183</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,16%</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12807,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>10579</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>23553</t>
+          <t>23297</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>15986</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>31868</t>
+          <t>31212</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>100247</t>
+          <t>100464</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>128013</t>
+          <t>128986</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>118058</t>
+          <t>118131</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>148519</t>
+          <t>146952</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>225217</t>
+          <t>226755</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>268272</t>
+          <t>268433</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -13389,7 +13389,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>145</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13469,12 +13469,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -13497,12 +13497,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52257</t>
+          <t>52353</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62777</t>
+          <t>63170</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13512,12 +13512,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71615</t>
+          <t>71316</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86392</t>
+          <t>85876</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127898</t>
+          <t>128936</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146291</t>
+          <t>145945</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13582,12 +13582,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -13615,7 +13615,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13680,12 +13680,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>828</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13695,12 +13695,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6854</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17240</t>
+          <t>17003</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13758,12 +13758,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>8649</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22670</t>
+          <t>22136</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13773,12 +13773,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13793,12 +13793,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18131</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35491</t>
+          <t>34675</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13808,12 +13808,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -14066,12 +14066,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43284</t>
+          <t>42712</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53707</t>
+          <t>53324</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14081,12 +14081,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14101,12 +14101,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49251</t>
+          <t>48852</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62576</t>
+          <t>61655</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14116,12 +14116,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14136,12 +14136,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94551</t>
+          <t>96989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112260</t>
+          <t>113074</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14151,12 +14151,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>84,2%</t>
         </is>
       </c>
     </row>
@@ -14179,12 +14179,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>582</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14194,12 +14194,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14249,12 +14249,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7906</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14264,12 +14264,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -14292,12 +14292,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6912</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>16533</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14307,12 +14307,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14327,12 +14327,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7888</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20877</t>
+          <t>21434</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14342,12 +14342,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14362,12 +14362,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17812</t>
+          <t>17919</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33784</t>
+          <t>33775</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14377,12 +14377,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -14635,12 +14635,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22078</t>
+          <t>22151</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27333</t>
+          <t>27254</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -14650,12 +14650,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23627</t>
+          <t>23673</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31924</t>
+          <t>32270</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14705,12 +14705,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>47920</t>
+          <t>47964</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>58448</t>
+          <t>57778</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -14720,12 +14720,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>90,81%</t>
         </is>
       </c>
     </row>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -14861,12 +14861,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>674</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14876,12 +14876,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14896,12 +14896,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10456</t>
+          <t>10638</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -14911,12 +14911,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>13170</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -14946,12 +14946,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15111,7 +15111,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15131,7 +15131,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -15204,12 +15204,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80417</t>
+          <t>79488</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94085</t>
+          <t>93860</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15239,12 +15239,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>88021</t>
+          <t>86889</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>109172</t>
+          <t>108876</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15254,12 +15254,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15274,12 +15274,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>173636</t>
+          <t>175369</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>199537</t>
+          <t>199023</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15289,12 +15289,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15337,7 +15337,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15357,7 +15357,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15387,12 +15387,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>504</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15407,7 +15407,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -15430,12 +15430,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16504</t>
+          <t>16743</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29954</t>
+          <t>30774</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15445,12 +15445,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15465,12 +15465,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15974</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37769</t>
+          <t>38428</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15500,12 +15500,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35880</t>
+          <t>36730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60908</t>
+          <t>60300</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15515,12 +15515,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>929</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>864</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -15773,12 +15773,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40565</t>
+          <t>40354</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55580</t>
+          <t>55685</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15788,12 +15788,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69111</t>
+          <t>68403</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88428</t>
+          <t>87964</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15823,12 +15823,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15843,12 +15843,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>116584</t>
+          <t>115419</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>140850</t>
+          <t>140709</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15858,12 +15858,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,95%</t>
         </is>
       </c>
     </row>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12234</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>27402</t>
+          <t>27615</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16034,12 +16034,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14772</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>34089</t>
+          <t>34797</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16049,12 +16049,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16069,12 +16069,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>30221</t>
+          <t>30521</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>54447</t>
+          <t>55197</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16084,12 +16084,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -16342,12 +16342,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36157</t>
+          <t>35623</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>43216</t>
+          <t>42848</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16357,12 +16357,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16377,12 +16377,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>30715</t>
+          <t>30770</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>40090</t>
+          <t>40008</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16392,12 +16392,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16412,12 +16412,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>69343</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>81508</t>
+          <t>81187</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16427,12 +16427,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -16568,12 +16568,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8708</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16583,12 +16583,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16603,12 +16603,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16618,12 +16618,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16638,12 +16638,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>19382</t>
+          <t>19656</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16653,12 +16653,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -16798,12 +16798,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>587</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16813,12 +16813,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16853,7 +16853,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16868,12 +16868,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16888,7 +16888,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>294401</t>
+          <t>295592</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>321592</t>
+          <t>321708</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16926,12 +16926,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16946,12 +16946,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>360930</t>
+          <t>362188</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>396866</t>
+          <t>398795</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -16961,12 +16961,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16981,12 +16981,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>666687</t>
+          <t>664681</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>713734</t>
+          <t>709676</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -16996,12 +16996,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>81,97%</t>
         </is>
       </c>
     </row>
@@ -17024,12 +17024,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -17059,12 +17059,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>3111</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11796</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17074,12 +17074,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17094,12 +17094,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>17801</t>
+          <t>17353</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -17137,12 +17137,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>59428</t>
+          <t>59254</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>84680</t>
+          <t>85208</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17152,47 +17152,47 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>15,29%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>21,98%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>90459</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>73312</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>108583</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>18,92%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
           <t>15,33%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>21,85%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>90459</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>74018</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>109263</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>18,92%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>15,48%</t>
-        </is>
-      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17207,12 +17207,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>139436</t>
+          <t>141432</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>184749</t>
+          <t>185661</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17222,12 +17222,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
